--- a/dcf/MA.xlsx
+++ b/dcf/MA.xlsx
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1109,25 +1109,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.06067301902940092</v>
+        <v>0.06065388784478447</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.06567301902940093</v>
+        <v>0.06565388784478447</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.07067301902940092</v>
+        <v>0.07065388784478446</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.07567301902940092</v>
+        <v>0.07565388784478447</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.08067301902940092</v>
+        <v>0.08065388784478447</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.08567301902940092</v>
+        <v>0.08565388784478446</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.09067301902940092</v>
+        <v>0.09065388784478447</v>
       </c>
     </row>
     <row r="5">
@@ -1135,25 +1135,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>523.298367677413</v>
+        <v>523.3768505060165</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>503.2692036908951</v>
+        <v>503.3440402261913</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>484.1677290496377</v>
+        <v>484.2391101451359</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>465.945515462085</v>
+        <v>466.0136210196379</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>448.5569067104023</v>
+        <v>448.6219063598799</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>431.9588470215856</v>
+        <v>432.0209007553134</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>416.1107208328859</v>
+        <v>416.1699795980728</v>
       </c>
     </row>
     <row r="6">
@@ -1161,25 +1161,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>557.0118112702871</v>
-      </c>
-      <c r="C6" s="53" t="n">
-        <v>535.4338386843622</v>
+        <v>557.0963755404846</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>535.5144500522873</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>514.8614644503641</v>
+        <v>514.9383305559506</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>495.2420045090381</v>
+        <v>495.315321049482</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>476.5257975730004</v>
+        <v>476.5957490451628</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>458.6660176657345</v>
+        <v>458.7327780590743</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>441.6184991213217</v>
+        <v>441.682232564887</v>
       </c>
     </row>
     <row r="7">
@@ -1187,25 +1187,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>590.7252548631614</v>
+        <v>590.8159005749528</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>567.5984736778292</v>
+        <v>567.6848598783833</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>545.5551998510905</v>
+        <v>545.6375509667655</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>524.5384935559911</v>
+        <v>524.617021079326</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>504.4946884355986</v>
+        <v>504.5695917304459</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>485.3731883098835</v>
+        <v>485.4446553628353</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>467.1262774097577</v>
+        <v>467.1944855317012</v>
       </c>
     </row>
     <row r="8">
@@ -1213,25 +1213,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>624.4386984560355</v>
+        <v>624.5354256094209</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>599.7631086712963</v>
+        <v>599.8552697044795</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>576.2489352518166</v>
+        <v>576.3367713775802</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>553.834982602944</v>
-      </c>
-      <c r="F8" s="53" t="n">
-        <v>532.4635792981967</v>
+        <v>553.9187211091701</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>532.5434344157289</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>512.0803589540325</v>
+        <v>512.1565326665963</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>492.6340556981936</v>
+        <v>492.7067384985153</v>
       </c>
     </row>
     <row r="9">
@@ -1239,25 +1239,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>658.1521420489096</v>
+        <v>658.2549506438891</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>631.9277436647633</v>
+        <v>632.0256795305753</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>606.9426706525428</v>
+        <v>607.0359917883949</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>583.131471649897</v>
+        <v>583.2204211390141</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>560.4324701607949</v>
-      </c>
-      <c r="G9" s="53" t="n">
-        <v>538.7875295981814</v>
+        <v>560.5172771010119</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>538.8684099703572</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>518.1418339866295</v>
+        <v>518.2189914653294</v>
       </c>
     </row>
     <row r="10">
@@ -1265,25 +1265,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>691.8655856417838</v>
+        <v>691.9744756783572</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>664.0923786582306</v>
+        <v>664.1960893566715</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>637.6364060532692</v>
+        <v>637.7352121992097</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>612.4279606968499</v>
+        <v>612.5221211688581</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>588.4013610233931</v>
+        <v>588.491119786295</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>565.4947002423304</v>
+        <v>565.5802872741182</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>543.6496122750655</v>
+        <v>543.7312444321436</v>
       </c>
     </row>
     <row r="11">
@@ -1291,25 +1291,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>725.5790292346582</v>
+        <v>725.6940007128253</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>696.2570136516975</v>
+        <v>696.3664991827675</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>668.3301414539956</v>
+        <v>668.4344326100244</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>641.724449743803</v>
+        <v>641.8238211987024</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>616.3702518859911</v>
+        <v>616.4649624715779</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>592.2018708864794</v>
+        <v>592.2921645778791</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>569.1573905635014</v>
+        <v>569.2434973989577</v>
       </c>
     </row>
     <row r="13">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>539.3900146484375</v>
+        <v>532.27001953125</v>
       </c>
     </row>
     <row r="14">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.07567301902940092</v>
+        <v>0.07565388784478447</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.024831080902874</v>
+        <v>1.02482872732297</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>539.3900146484375</v>
+        <v>532.27001953125</v>
       </c>
     </row>
     <row r="49">
@@ -24592,13 +24592,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>553.834982602944</v>
+        <v>553.9187211091701</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>740.3011797019341</v>
+        <v>740.4161403027524</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>410.5108187146803</v>
+        <v>410.5708094925555</v>
       </c>
     </row>
     <row r="59">
